--- a/src/xlsx/data.xlsx
+++ b/src/xlsx/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/PKMN_G1/pokeredCHS/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/Pokemon_Projects/pokeredCHS/src/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161E2EC6-84FA-F04F-8A03-CBF01510D83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FA5F50-7DAC-0C48-9987-35942053953A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20480" activeTab="6" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2947" uniqueCount="2176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2947" uniqueCount="2177">
   <si>
     <t>data/pokemon/names.asm</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7543,11 +7543,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>v110@</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 第   次 登入名人堂@</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"POKéMANIAC@"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v120@</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7741,9 +7745,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7781,7 +7785,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7887,7 +7891,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8029,7 +8033,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14176,7 +14180,7 @@
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="6" t="s">
-        <v>1244</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -14459,7 +14463,7 @@
         <v>1162</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2046</v>
+        <v>1980</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>1729</v>
@@ -15866,7 +15870,7 @@
         <v>2139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -17236,7 +17240,7 @@
         <v>1520</v>
       </c>
       <c r="C192" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="193" spans="1:6">
